--- a/static/excel/CSCO_model.xlsx
+++ b/static/excel/CSCO_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="P&amp;L" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Balance Sheet" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Cash Flow" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Ratios &amp; FCF" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Segments" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="WACC" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="DCF" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Scorecard" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P&amp;L" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ratios &amp; FCF" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Segments" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WACC" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scorecard" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -7353,11 +7353,11 @@
         </is>
       </c>
       <c r="B5" s="43" t="n">
-        <v>456331.143142</v>
+        <v>466877.357564</v>
       </c>
       <c r="C5" s="44" t="inlineStr">
         <is>
-          <t>FMP marketCap  |  price $115.53</t>
+          <t>FMP marketCap  |  price $118.2</t>
         </is>
       </c>
     </row>
@@ -7439,11 +7439,11 @@
         </is>
       </c>
       <c r="B12" s="46" t="n">
-        <v>0.0446</v>
+        <v>0.0457</v>
       </c>
       <c r="C12" s="44" t="inlineStr">
         <is>
-          <t>FRED series DGS10  |  latest: 2026-05-13</t>
+          <t>FRED series DGS10  |  latest: 2026-05-20</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
         </is>
       </c>
       <c r="B13" s="48" t="n">
-        <v>0.0446</v>
+        <v>0.0457</v>
       </c>
       <c r="C13" s="49" t="inlineStr">
         <is>
@@ -7526,7 +7526,7 @@
         </is>
       </c>
       <c r="B19" s="50" t="n">
-        <v>1.056</v>
+        <v>1.055</v>
       </c>
       <c r="C19" s="44">
         <f> unlevered × (1 + (1 − t) × D/E)</f>
@@ -7540,7 +7540,7 @@
         </is>
       </c>
       <c r="B20" s="51" t="n">
-        <v>0.97</v>
+        <v>0.969</v>
       </c>
       <c r="C20" s="49" t="inlineStr">
         <is>
@@ -7714,11 +7714,11 @@
         </is>
       </c>
       <c r="B35" s="46" t="n">
-        <v>0.0554</v>
+        <v>0.05650000000000001</v>
       </c>
       <c r="C35" s="44" t="inlineStr">
         <is>
-          <t>Rf 4.46% + spread 1.08%</t>
+          <t>Rf 4.57% + spread 1.08%</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
         </is>
       </c>
       <c r="B37" s="48" t="n">
-        <v>0.0547</v>
+        <v>0.0552</v>
       </c>
       <c r="C37" s="49" t="inlineStr">
         <is>
@@ -8181,13 +8181,13 @@
         <v/>
       </c>
       <c r="G7" s="72" t="n">
-        <v>0.0872</v>
+        <v>0.1103</v>
       </c>
       <c r="H7" s="72" t="n">
-        <v>0.0577</v>
+        <v>0.0915</v>
       </c>
       <c r="I7" s="72" t="n">
-        <v>0.0473</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="J7" s="73">
         <f>I7</f>
@@ -8531,13 +8531,13 @@
         <v/>
       </c>
       <c r="G15" s="78" t="n">
-        <v>61592.9</v>
+        <v>62901.4</v>
       </c>
       <c r="H15" s="78" t="n">
-        <v>65143.9</v>
+        <v>68655.5</v>
       </c>
       <c r="I15" s="78" t="n">
-        <v>68224.10000000001</v>
+        <v>73298.39999999999</v>
       </c>
       <c r="J15" s="79">
         <f>I15*(1+J7)</f>
@@ -8565,17 +8565,17 @@
       </c>
       <c r="G16" s="83" t="inlineStr">
         <is>
-          <t>59,767 — 62,335</t>
+          <t>61,755 — 63,334</t>
         </is>
       </c>
       <c r="H16" s="83" t="inlineStr">
         <is>
-          <t>62,982 — 67,286</t>
+          <t>64,458 — 71,695</t>
         </is>
       </c>
       <c r="I16" s="83" t="inlineStr">
         <is>
-          <t>68,167 — 68,282</t>
+          <t>73,182 — 73,414</t>
         </is>
       </c>
       <c r="J16" s="84" t="inlineStr">
@@ -8606,13 +8606,13 @@
         </is>
       </c>
       <c r="G17" s="86" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H17" s="86" t="n">
         <v>19</v>
       </c>
       <c r="I17" s="86" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J17" s="84" t="inlineStr">
         <is>
@@ -8733,13 +8733,13 @@
         <v/>
       </c>
       <c r="G20" s="78" t="n">
-        <v>18584.7</v>
+        <v>18979.5</v>
       </c>
       <c r="H20" s="78" t="n">
-        <v>19656.1</v>
+        <v>20715.7</v>
       </c>
       <c r="I20" s="78" t="n">
-        <v>20585.5</v>
+        <v>22116.6</v>
       </c>
       <c r="J20" s="79">
         <f>J15*J8</f>
@@ -8767,17 +8767,17 @@
       </c>
       <c r="G21" s="83" t="inlineStr">
         <is>
-          <t>18,034 — 18,809</t>
+          <t>18,634 — 19,110</t>
         </is>
       </c>
       <c r="H21" s="83" t="inlineStr">
         <is>
-          <t>19,004 — 20,302</t>
+          <t>19,449 — 21,633</t>
         </is>
       </c>
       <c r="I21" s="83" t="inlineStr">
         <is>
-          <t>20,568 — 20,603</t>
+          <t>22,082 — 22,152</t>
         </is>
       </c>
       <c r="J21" s="84" t="inlineStr">
@@ -9967,7 +9967,7 @@
         </is>
       </c>
       <c r="B61" s="114" t="n">
-        <v>115.53</v>
+        <v>118.2</v>
       </c>
       <c r="C61" s="106" t="n"/>
       <c r="D61" s="106" t="n"/>
@@ -10067,7 +10067,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="116" t="inlineStr">
         <is>
-          <t>JS SCORECARD — CSCO  |  Master Prompt v2  |  15 May 2026  |  Sector bucket: Stable Compounder</t>
+          <t>JS SCORECARD — CSCO  |  Master Prompt v2  |  22 May 2026  |  Sector bucket: Stable Compounder</t>
         </is>
       </c>
     </row>
@@ -10200,7 +10200,7 @@
       </c>
       <c r="D9" s="132" t="inlineStr">
         <is>
-          <t>GM 64.9% ✓ (&gt;40%)  |  GM trend +2.4% ✓ (&gt;+1pp)  |  ROIC-WACC +11.2% ✓ (&gt;+5pp)  |  Rev consistency σ=5.8% ✓ (&lt;8%)  [4/4 indicators positive — proxy score]</t>
+          <t>GM 64.9% ✓ (&gt;40%)  |  GM trend +2.4% ✓ (&gt;+1pp)  |  ROIC-WACC +8.0% ✓ (&gt;+5pp)  |  Rev consistency σ=5.8% ✓ (&lt;8%)  [4/4 indicators positive — proxy score]</t>
         </is>
       </c>
       <c r="E9" s="133" t="inlineStr">
@@ -10217,7 +10217,7 @@
       </c>
       <c r="H9" s="136" t="inlineStr">
         <is>
-          <t>GM 64.9% ✓ (&gt;40%)  |  GM trend +2.4% ✓ (&gt;+1pp)  |  ROIC-WACC +11.2% ✓ (&gt;+5pp)  |  Rev consistency σ=5.8% ✓ (&lt;8%)  [4/4 indicators positive — proxy score]</t>
+          <t>GM 64.9% ✓ (&gt;40%)  |  GM trend +2.4% ✓ (&gt;+1pp)  |  ROIC-WACC +8.0% ✓ (&gt;+5pp)  |  Rev consistency σ=5.8% ✓ (&lt;8%)  [4/4 indicators positive — proxy score]</t>
         </is>
       </c>
     </row>
@@ -10267,7 +10267,7 @@
       </c>
       <c r="D11" s="132" t="inlineStr">
         <is>
-          <t>ROIC trend -10.6% ✗ (≥-2pp)  |  GM maintained +2.4% ✓  |  Op margin -6.3% ✗ (≥-2pp)  |  Capital returns HIGH ✓  |  Share count -1.5%/yr ✓ (net buyback)  |  Goodwill/Equity 126% ✗ (&lt;40%)  [3/6 indicators positive — proxy score]</t>
+          <t>ROIC trend -10.6% ✗ (&gt;=-2pp)  |  GM maintained +2.4% ✓  |  Op margin -6.3% ✗ (≥-2pp)  |  Capital returns HIGH ✓  |  Share count -1.5%/yr ✓ (net buyback)  |  Goodwill/Equity 126% ✗ (&lt;40%)  [3/6 indicators positive — proxy score]</t>
         </is>
       </c>
       <c r="E11" s="137" t="inlineStr">
@@ -10284,7 +10284,7 @@
       </c>
       <c r="H11" s="136" t="inlineStr">
         <is>
-          <t>ROIC trend -10.6% ✗ (≥-2pp)  |  GM maintained +2.4% ✓  |  Op margin -6.3% ✗ (≥-2pp)  |  Capital returns HIGH ✓  |  Share count -1.5%/yr ✓ (net buyback)  |  Goodwill/Equity 126% ✗ (&lt;40%)  [3/6 indicators positive — proxy score]</t>
+          <t>ROIC trend -10.6% ✗ (&gt;=-2pp)  |  GM maintained +2.4% ✓  |  Op margin -6.3% ✗ (≥-2pp)  |  Capital returns HIGH ✓  |  Share count -1.5%/yr ✓ (net buyback)  |  Goodwill/Equity 126% ✗ (&lt;40%)  [3/6 indicators positive — proxy score]</t>
         </is>
       </c>
     </row>
@@ -10357,7 +10357,7 @@
         </is>
       </c>
       <c r="F14" s="134" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G14" s="135">
         <f>IF(F14="",0,C14*F14*10)</f>
@@ -10540,16 +10540,16 @@
       </c>
       <c r="D20" s="132" t="inlineStr">
         <is>
-          <t>Rev growth σ=5.8%  |  Op margin σ=2.4%  [proxy — lower σ = lower risk = higher score]</t>
-        </is>
-      </c>
-      <c r="E20" s="138" t="inlineStr">
-        <is>
-          <t>MOD-HIGH</t>
+          <t>Rev growth σ=5.8%  |  OM trend -5.0%, σ=2.4%  [quality = direction + stability]</t>
+        </is>
+      </c>
+      <c r="E20" s="137" t="inlineStr">
+        <is>
+          <t>MOD-LOW</t>
         </is>
       </c>
       <c r="F20" s="134" t="n">
-        <v>6.67</v>
+        <v>3.33</v>
       </c>
       <c r="G20" s="135">
         <f>IF(F20="",0,C20*F20*10)</f>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="H20" s="136" t="inlineStr">
         <is>
-          <t>Rev growth σ=5.8%  |  Op margin σ=2.4%  [proxy — lower σ = lower risk = higher score]</t>
+          <t>Rev growth σ=5.8%  |  OM trend -5.0%, σ=2.4%  [quality = direction + stability]</t>
         </is>
       </c>
     </row>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="D22" s="132" t="inlineStr">
         <is>
-          <t>Current 26.8x  |  5yr avg 20.1x  |  DCF-implied 23.2x  [+33% vs benchmark]</t>
+          <t>Current 26.8x  |  5yr avg 20.1x  |  DCF-implied 25.3x [ref only — not used as benchmark]  [+33% vs benchmark]  [trail=2.00 | no_fwd_data(fallback) | abs=4.0 → blended 40/40/20=2.40]  PEG≈839.50 (trailing_pe=26.8x / rev_cagr=3%, revenue proxy)</t>
         </is>
       </c>
       <c r="E22" s="139" t="inlineStr">
@@ -10593,7 +10593,7 @@
         </is>
       </c>
       <c r="F22" s="134" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="G22" s="135">
         <f>IF(F22="",0,C22*F22*10)</f>
@@ -10601,7 +10601,7 @@
       </c>
       <c r="H22" s="136" t="inlineStr">
         <is>
-          <t>Current 26.8x  |  5yr avg 20.1x  |  DCF-implied 23.2x  [+33% vs benchmark]</t>
+          <t>Current 26.8x  |  5yr avg 20.1x  |  DCF-implied 25.3x [ref only — not used as benchmark]  [+33% vs benchmark]  [trail=2.00 | no_fwd_data(fallback) | abs=4.0 → blended 40/40/20=2.40]  PEG≈839.50 (trailing_pe=26.8x / rev_cagr=3%, revenue proxy)</t>
         </is>
       </c>
     </row>
@@ -10621,7 +10621,7 @@
       </c>
       <c r="D23" s="132" t="inlineStr">
         <is>
-          <t>Current 20.6x  |  5yr avg 16.3x  |  DCF-implied 17.8x  [+26% vs benchmark]</t>
+          <t>Current 20.6x  |  5yr avg 16.3x  |  DCF-implied 19.4x [ref only — not used as benchmark]  [+26% vs benchmark]  [trail=2.83 | no_fwd_data(fallback) | abs=7.5 → blended 40/40/20=3.77]</t>
         </is>
       </c>
       <c r="E23" s="139" t="inlineStr">
@@ -10630,7 +10630,7 @@
         </is>
       </c>
       <c r="F23" s="134" t="n">
-        <v>2.83</v>
+        <v>3.77</v>
       </c>
       <c r="G23" s="135">
         <f>IF(F23="",0,C23*F23*10)</f>
@@ -10638,7 +10638,7 @@
       </c>
       <c r="H23" s="136" t="inlineStr">
         <is>
-          <t>Current 20.6x  |  5yr avg 16.3x  |  DCF-implied 17.8x  [+26% vs benchmark]</t>
+          <t>Current 20.6x  |  5yr avg 16.3x  |  DCF-implied 19.4x [ref only — not used as benchmark]  [+26% vs benchmark]  [trail=2.83 | no_fwd_data(fallback) | abs=7.5 → blended 40/40/20=3.77]</t>
         </is>
       </c>
     </row>

--- a/static/excel/CSCO_model.xlsx
+++ b/static/excel/CSCO_model.xlsx
@@ -7353,11 +7353,11 @@
         </is>
       </c>
       <c r="B5" s="43" t="n">
-        <v>466877.357564</v>
+        <v>474588.151745</v>
       </c>
       <c r="C5" s="44" t="inlineStr">
         <is>
-          <t>FMP marketCap  |  price $118.2</t>
+          <t>FMP marketCap  |  price $120.41</t>
         </is>
       </c>
     </row>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="C12" s="44" t="inlineStr">
         <is>
-          <t>FRED series DGS10  |  latest: 2026-05-20</t>
+          <t>FRED series DGS10  |  latest: 2026-05-21</t>
         </is>
       </c>
     </row>
@@ -7526,7 +7526,7 @@
         </is>
       </c>
       <c r="B19" s="50" t="n">
-        <v>1.055</v>
+        <v>1.054</v>
       </c>
       <c r="C19" s="44">
         <f> unlevered × (1 + (1 − t) × D/E)</f>
@@ -7809,16 +7809,16 @@
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="54" t="inlineStr">
         <is>
-          <t>WACC  =  (E/V × Re)  +  (D/V × Rd × (1 − t))</t>
+          <t>WACC  =  MAX(8.5%, (E/V × Re) + (D/V × Rd × (1 − t)))</t>
         </is>
       </c>
       <c r="B44" s="55">
-        <f>B8*B28+B9*B37*(1-B41)</f>
+        <f>MAX(0.085, B8*B28+B9*B37*(1-B41))</f>
         <v/>
       </c>
       <c r="C44" s="56" t="inlineStr">
         <is>
-          <t>Used as discount rate in DCF tab</t>
+          <t>Floored 8.5% (D-001); raw formula below</t>
         </is>
       </c>
     </row>
@@ -8565,12 +8565,12 @@
       </c>
       <c r="G16" s="83" t="inlineStr">
         <is>
-          <t>61,755 — 63,334</t>
+          <t>61,899 — 63,132</t>
         </is>
       </c>
       <c r="H16" s="83" t="inlineStr">
         <is>
-          <t>64,458 — 71,695</t>
+          <t>64,110 — 71,309</t>
         </is>
       </c>
       <c r="I16" s="83" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="G21" s="83" t="inlineStr">
         <is>
-          <t>18,634 — 19,110</t>
+          <t>18,677 — 19,049</t>
         </is>
       </c>
       <c r="H21" s="83" t="inlineStr">
         <is>
-          <t>19,449 — 21,633</t>
+          <t>19,344 — 21,516</t>
         </is>
       </c>
       <c r="I21" s="83" t="inlineStr">
@@ -9451,7 +9451,7 @@
         </is>
       </c>
       <c r="B38" s="103" t="n">
-        <v>10</v>
+        <v>11.4</v>
       </c>
       <c r="C38" s="101" t="n"/>
       <c r="D38" s="101" t="n"/>
@@ -9465,7 +9465,7 @@
       <c r="L38" s="101" t="n"/>
       <c r="M38" s="75" t="inlineStr">
         <is>
-          <t>Growth tier: LOW (3.4% 3yr avg rev growth).  Bear 8x / Base 10x / Bull 12x.  Override manually if needed.</t>
+          <t>Growth tier: LOW (3.4% 3yr avg rev growth).  Bear 9x / Base 11x / Bull 14x.  Override manually if needed.</t>
         </is>
       </c>
     </row>
@@ -9967,7 +9967,7 @@
         </is>
       </c>
       <c r="B61" s="114" t="n">
-        <v>118.2</v>
+        <v>120.41</v>
       </c>
       <c r="C61" s="106" t="n"/>
       <c r="D61" s="106" t="n"/>
@@ -10067,7 +10067,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="116" t="inlineStr">
         <is>
-          <t>JS SCORECARD — CSCO  |  Master Prompt v2  |  22 May 2026  |  Sector bucket: Stable Compounder</t>
+          <t>JS SCORECARD — CSCO  |  Master Prompt v2  |  25 May 2026  |  Sector bucket: Stable Compounder</t>
         </is>
       </c>
     </row>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="D22" s="132" t="inlineStr">
         <is>
-          <t>Current 26.8x  |  5yr avg 20.1x  |  DCF-implied 25.3x [ref only — not used as benchmark]  [+33% vs benchmark]  [trail=2.00 | no_fwd_data(fallback) | abs=4.0 → blended 40/40/20=2.40]  PEG≈839.50 (trailing_pe=26.8x / rev_cagr=3%, revenue proxy)</t>
+          <t>Current 26.8x  |  5yr avg 20.1x  |  DCF-implied 25.3x [ref only — not used as benchmark]  [+33% vs benchmark]  [trail=2.00 | fwd_pe=28.2x→1.16 | abs=4.0 → blended 40/40/20=2.07]  PEG=42.20 (fwd_pe=28.2x / eps_growth=67%)  [revision:Strong upgrade cycle→+0.50]</t>
         </is>
       </c>
       <c r="E22" s="139" t="inlineStr">
@@ -10593,7 +10593,7 @@
         </is>
       </c>
       <c r="F22" s="134" t="n">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
       <c r="G22" s="135">
         <f>IF(F22="",0,C22*F22*10)</f>
@@ -10601,7 +10601,7 @@
       </c>
       <c r="H22" s="136" t="inlineStr">
         <is>
-          <t>Current 26.8x  |  5yr avg 20.1x  |  DCF-implied 25.3x [ref only — not used as benchmark]  [+33% vs benchmark]  [trail=2.00 | no_fwd_data(fallback) | abs=4.0 → blended 40/40/20=2.40]  PEG≈839.50 (trailing_pe=26.8x / rev_cagr=3%, revenue proxy)</t>
+          <t>Current 26.8x  |  5yr avg 20.1x  |  DCF-implied 25.3x [ref only — not used as benchmark]  [+33% vs benchmark]  [trail=2.00 | fwd_pe=28.2x→1.16 | abs=4.0 → blended 40/40/20=2.07]  PEG=42.20 (fwd_pe=28.2x / eps_growth=67%)  [revision:Strong upgrade cycle→+0.50]</t>
         </is>
       </c>
     </row>
@@ -10621,7 +10621,7 @@
       </c>
       <c r="D23" s="132" t="inlineStr">
         <is>
-          <t>Current 20.6x  |  5yr avg 16.3x  |  DCF-implied 19.4x [ref only — not used as benchmark]  [+26% vs benchmark]  [trail=2.83 | no_fwd_data(fallback) | abs=7.5 → blended 40/40/20=3.77]</t>
+          <t>Current 20.6x  |  5yr avg 16.3x  |  DCF-implied 19.4x [ref only — not used as benchmark]  [+26% vs benchmark]  [trail=2.83 | fwd_pfcf=32.5x→0.00 | abs=7.5 → blended 40/40/20=2.63]</t>
         </is>
       </c>
       <c r="E23" s="139" t="inlineStr">
@@ -10630,7 +10630,7 @@
         </is>
       </c>
       <c r="F23" s="134" t="n">
-        <v>3.77</v>
+        <v>2.63</v>
       </c>
       <c r="G23" s="135">
         <f>IF(F23="",0,C23*F23*10)</f>
@@ -10638,7 +10638,7 @@
       </c>
       <c r="H23" s="136" t="inlineStr">
         <is>
-          <t>Current 20.6x  |  5yr avg 16.3x  |  DCF-implied 19.4x [ref only — not used as benchmark]  [+26% vs benchmark]  [trail=2.83 | no_fwd_data(fallback) | abs=7.5 → blended 40/40/20=3.77]</t>
+          <t>Current 20.6x  |  5yr avg 16.3x  |  DCF-implied 19.4x [ref only — not used as benchmark]  [+26% vs benchmark]  [trail=2.83 | fwd_pfcf=32.5x→0.00 | abs=7.5 → blended 40/40/20=2.63]</t>
         </is>
       </c>
     </row>

--- a/static/excel/CSCO_model.xlsx
+++ b/static/excel/CSCO_model.xlsx
@@ -7439,11 +7439,11 @@
         </is>
       </c>
       <c r="B12" s="46" t="n">
-        <v>0.0457</v>
+        <v>0.04559999999999999</v>
       </c>
       <c r="C12" s="44" t="inlineStr">
         <is>
-          <t>FRED series DGS10  |  latest: 2026-05-21</t>
+          <t>FRED series DGS10  |  latest: 2026-05-22</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
         </is>
       </c>
       <c r="B13" s="48" t="n">
-        <v>0.0457</v>
+        <v>0.0456</v>
       </c>
       <c r="C13" s="49" t="inlineStr">
         <is>
@@ -7653,25 +7653,27 @@
       </c>
       <c r="B31" s="53" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C31" s="44" t="inlineStr">
         <is>
-          <t>FMP /ratings endpoint</t>
+          <t>User input</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="17" t="inlineStr">
         <is>
-          <t>FRED matched yield</t>
-        </is>
-      </c>
-      <c r="B32" s="53" t="n"/>
+          <t>FRED matched yield  (rating-tier index)</t>
+        </is>
+      </c>
+      <c r="B32" s="46" t="n">
+        <v>0.0507</v>
+      </c>
       <c r="C32" s="44" t="inlineStr">
         <is>
-          <t>No rating returned — FRED method not applicable</t>
+          <t>FRED BAMLC0A3CAEY — A</t>
         </is>
       </c>
     </row>
@@ -7714,11 +7716,11 @@
         </is>
       </c>
       <c r="B35" s="46" t="n">
-        <v>0.05650000000000001</v>
+        <v>0.05639999999999999</v>
       </c>
       <c r="C35" s="44" t="inlineStr">
         <is>
-          <t>Rf 4.57% + spread 1.08%</t>
+          <t>Rf 4.56% + spread 1.08%</t>
         </is>
       </c>
     </row>
@@ -7744,11 +7746,11 @@
         </is>
       </c>
       <c r="B37" s="48" t="n">
-        <v>0.0552</v>
+        <v>0.0537</v>
       </c>
       <c r="C37" s="49" t="inlineStr">
         <is>
-          <t>Default = average of 2 source(s) above — override freely</t>
+          <t>Default = average of 3 source(s) above — override freely</t>
         </is>
       </c>
     </row>
@@ -10067,7 +10069,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="116" t="inlineStr">
         <is>
-          <t>JS SCORECARD — CSCO  |  Master Prompt v2  |  25 May 2026  |  Sector bucket: Stable Compounder</t>
+          <t>JS SCORECARD — CSCO  |  Master Prompt v2  |  27 May 2026  |  Sector bucket: Stable Compounder</t>
         </is>
       </c>
     </row>
@@ -10584,7 +10586,7 @@
       </c>
       <c r="D22" s="132" t="inlineStr">
         <is>
-          <t>Current 26.8x  |  5yr avg 20.1x  |  DCF-implied 25.3x [ref only — not used as benchmark]  [+33% vs benchmark]  [trail=2.00 | fwd_pe=28.2x→1.16 | abs=4.0 → blended 40/40/20=2.07]  PEG=42.20 (fwd_pe=28.2x / eps_growth=67%)  [revision:Strong upgrade cycle→+0.50]</t>
+          <t>Fwd P/E 28.2x (scoring basis)  |  5yr avg 21.4x  |  DCF-implied 25.4x [ref only — not used as benchmark]  [+32% vs benchmark]  [trail=2.19 | fwd_pe=28.2x→2.19 | abs=4.0 → blended 40/40/20=2.55]  PEG=42.20 (fwd_pe=28.2x / eps_growth=67%)  [revision:Strong upgrade cycle→+0.50]</t>
         </is>
       </c>
       <c r="E22" s="139" t="inlineStr">
@@ -10593,7 +10595,7 @@
         </is>
       </c>
       <c r="F22" s="134" t="n">
-        <v>2.57</v>
+        <v>3.05</v>
       </c>
       <c r="G22" s="135">
         <f>IF(F22="",0,C22*F22*10)</f>
@@ -10601,7 +10603,7 @@
       </c>
       <c r="H22" s="136" t="inlineStr">
         <is>
-          <t>Current 26.8x  |  5yr avg 20.1x  |  DCF-implied 25.3x [ref only — not used as benchmark]  [+33% vs benchmark]  [trail=2.00 | fwd_pe=28.2x→1.16 | abs=4.0 → blended 40/40/20=2.07]  PEG=42.20 (fwd_pe=28.2x / eps_growth=67%)  [revision:Strong upgrade cycle→+0.50]</t>
+          <t>Fwd P/E 28.2x (scoring basis)  |  5yr avg 21.4x  |  DCF-implied 25.4x [ref only — not used as benchmark]  [+32% vs benchmark]  [trail=2.19 | fwd_pe=28.2x→2.19 | abs=4.0 → blended 40/40/20=2.55]  PEG=42.20 (fwd_pe=28.2x / eps_growth=67%)  [revision:Strong upgrade cycle→+0.50]</t>
         </is>
       </c>
     </row>
@@ -10621,16 +10623,16 @@
       </c>
       <c r="D23" s="132" t="inlineStr">
         <is>
-          <t>Current 20.6x  |  5yr avg 16.3x  |  DCF-implied 19.4x [ref only — not used as benchmark]  [+26% vs benchmark]  [trail=2.83 | fwd_pfcf=32.5x→0.00 | abs=7.5 → blended 40/40/20=2.63]</t>
-        </is>
-      </c>
-      <c r="E23" s="139" t="inlineStr">
-        <is>
-          <t>LOW</t>
+          <t>Current 20.6x  |  5yr avg 17.2x  |  DCF-implied 19.4x [ref only — not used as benchmark]  [+20% vs benchmark]  [trail=3.84 | fwd_pfcf=32.5x→0.00 | abs=7.5 → blended 40/40/20=3.03]</t>
+        </is>
+      </c>
+      <c r="E23" s="137" t="inlineStr">
+        <is>
+          <t>MOD-LOW</t>
         </is>
       </c>
       <c r="F23" s="134" t="n">
-        <v>2.63</v>
+        <v>3.03</v>
       </c>
       <c r="G23" s="135">
         <f>IF(F23="",0,C23*F23*10)</f>
@@ -10638,7 +10640,7 @@
       </c>
       <c r="H23" s="136" t="inlineStr">
         <is>
-          <t>Current 20.6x  |  5yr avg 16.3x  |  DCF-implied 19.4x [ref only — not used as benchmark]  [+26% vs benchmark]  [trail=2.83 | fwd_pfcf=32.5x→0.00 | abs=7.5 → blended 40/40/20=2.63]</t>
+          <t>Current 20.6x  |  5yr avg 17.2x  |  DCF-implied 19.4x [ref only — not used as benchmark]  [+20% vs benchmark]  [trail=3.84 | fwd_pfcf=32.5x→0.00 | abs=7.5 → blended 40/40/20=3.03]</t>
         </is>
       </c>
     </row>
